--- a/file/personal/人生规划执行表.xlsx
+++ b/file/personal/人生规划执行表.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23320" windowHeight="12720" activeTab="2"/>
+    <workbookView windowWidth="22340" windowHeight="13160" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="好习惯" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>分类</t>
   </si>
@@ -166,6 +166,30 @@
     <t>是否反思</t>
   </si>
   <si>
+    <t>身体</t>
+  </si>
+  <si>
+    <t>面部管理</t>
+  </si>
+  <si>
+    <t>去掉脸上斑点、痘痘</t>
+  </si>
+  <si>
+    <t>整理一套适合自己的日常护理方案</t>
+  </si>
+  <si>
+    <t>鼻炎质量</t>
+  </si>
+  <si>
+    <t>做一套日常保养方案</t>
+  </si>
+  <si>
+    <t>心脏保养</t>
+  </si>
+  <si>
+    <t>做一套日常心脏保养方案</t>
+  </si>
+  <si>
     <t>关注生活/家庭</t>
   </si>
   <si>
@@ -181,6 +205,12 @@
     <t>已完成</t>
   </si>
   <si>
+    <t>全家做飞机旅游一次</t>
+  </si>
+  <si>
+    <t>进行中</t>
+  </si>
+  <si>
     <t>关注事业</t>
   </si>
   <si>
@@ -191,9 +221,6 @@
   </si>
   <si>
     <t>不用担心失业，工作强度不是太大（事业编/国企）</t>
-  </si>
-  <si>
-    <t>进行中</t>
   </si>
   <si>
     <t>副业</t>
@@ -233,9 +260,6 @@
     <t>P1</t>
   </si>
   <si>
-    <t>重要紧急</t>
-  </si>
-  <si>
     <t>刷6套试卷</t>
   </si>
   <si>
@@ -257,9 +281,6 @@
     <t>P2</t>
   </si>
   <si>
-    <t>重要不紧急</t>
-  </si>
-  <si>
     <t>扩展平台与通道</t>
   </si>
   <si>
@@ -269,7 +290,22 @@
     <t>参加一次编制考试</t>
   </si>
   <si>
-    <t>探索新的RPA自动化领域</t>
+    <t>实现副业盈利</t>
+  </si>
+  <si>
+    <t>关注下半年招生</t>
+  </si>
+  <si>
+    <t>报名并参加9/10月份的事业单位考试</t>
+  </si>
+  <si>
+    <t>关注其它单位自主招生情况</t>
+  </si>
+  <si>
+    <t>保住工作</t>
+  </si>
+  <si>
+    <t>保证年终评审不能低于B</t>
   </si>
 </sst>
 </file>
@@ -453,7 +489,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,13 +516,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="6" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -517,12 +547,6 @@
       </gradientFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
       <gradientFill degree="270">
         <stop position="0">
           <color rgb="FFA5E5FF"/>
@@ -734,7 +758,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -803,6 +827,21 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="18"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="18"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="18"/>
       </left>
       <right style="thin">
@@ -846,17 +885,30 @@
     </border>
     <border>
       <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="13"/>
       </left>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="18"/>
+        <color indexed="13"/>
       </top>
-      <bottom style="thin">
-        <color indexed="18"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -869,9 +921,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1187,7 +1237,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="26" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1199,119 +1249,119 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1339,118 +1389,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2658,199 +2738,199 @@
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultColWidth="9.64423076923077" defaultRowHeight="13" customHeight="1" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="19.0673076923077" style="18" customWidth="1"/>
-    <col min="2" max="2" width="22.75" style="18" customWidth="1"/>
-    <col min="3" max="3" width="38.6153846153846" style="18" customWidth="1"/>
-    <col min="4" max="16384" width="16.3557692307692" style="18" customWidth="1"/>
+    <col min="1" max="1" width="19.0673076923077" style="25" customWidth="1"/>
+    <col min="2" max="2" width="22.75" style="25" customWidth="1"/>
+    <col min="3" max="3" width="38.6153846153846" style="25" customWidth="1"/>
+    <col min="4" max="16384" width="16.3557692307692" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.55" customHeight="1" spans="1:3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="42" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" ht="13.55" customHeight="1" spans="1:3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="34"/>
+      <c r="C2" s="45"/>
     </row>
     <row r="3" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A3" s="35"/>
-      <c r="B3" s="36" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="37"/>
+      <c r="C3" s="48"/>
     </row>
     <row r="4" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36" t="s">
+      <c r="A4" s="46"/>
+      <c r="B4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="37"/>
+      <c r="C4" s="48"/>
     </row>
     <row r="5" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A5" s="35"/>
-      <c r="B5" s="36" t="s">
+      <c r="A5" s="46"/>
+      <c r="B5" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="48" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A6" s="35"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="46"/>
+      <c r="B6" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="48" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="37"/>
+      <c r="C7" s="48"/>
     </row>
     <row r="8" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A8" s="39"/>
-      <c r="B8" s="36" t="s">
+      <c r="A8" s="50"/>
+      <c r="B8" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="37"/>
+      <c r="C8" s="48"/>
     </row>
     <row r="9" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A9" s="39"/>
-      <c r="B9" s="40" t="s">
+      <c r="A9" s="50"/>
+      <c r="B9" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="48" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="52" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A11" s="39"/>
-      <c r="B11" s="40" t="s">
+      <c r="A11" s="50"/>
+      <c r="B11" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="48" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A12" s="39"/>
-      <c r="B12" s="40" t="s">
+      <c r="A12" s="50"/>
+      <c r="B12" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="48" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="13" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="37"/>
+      <c r="C13" s="48"/>
     </row>
     <row r="14" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A14" s="39"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="37"/>
+      <c r="A14" s="50"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="48"/>
     </row>
     <row r="15" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A15" s="39"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="37"/>
+      <c r="A15" s="50"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="48"/>
     </row>
     <row r="16" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="48" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A17" s="42"/>
-      <c r="B17" s="43" t="s">
+      <c r="A17" s="53"/>
+      <c r="B17" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="C17" s="55" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A18" s="42"/>
-      <c r="B18" s="43" t="s">
+      <c r="A18" s="53"/>
+      <c r="B18" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="45" t="s">
+      <c r="C18" s="56" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" ht="13.35" customHeight="1" spans="1:3">
-      <c r="A19" s="42"/>
-      <c r="B19" s="43" t="s">
+      <c r="A19" s="53"/>
+      <c r="B19" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="45" t="s">
+      <c r="C19" s="56" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="42"/>
-      <c r="B20" s="43" t="s">
+      <c r="A20" s="53"/>
+      <c r="B20" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="36" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="42"/>
-      <c r="B21" s="43" t="s">
+      <c r="A21" s="53"/>
+      <c r="B21" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="36" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="42"/>
-      <c r="B22" s="43" t="s">
+      <c r="A22" s="53"/>
+      <c r="B22" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="36" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2873,339 +2953,277 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="9.64423076923077" defaultRowHeight="13" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="12.4519230769231" style="18" customWidth="1"/>
-    <col min="2" max="2" width="22.0480769230769" style="18" customWidth="1"/>
-    <col min="3" max="3" width="37.2980769230769" style="18" customWidth="1"/>
-    <col min="4" max="4" width="10.8461538461538" style="18" customWidth="1"/>
-    <col min="5" max="5" width="14.5865384615385" style="18" customWidth="1"/>
-    <col min="6" max="16384" width="6" style="18" customWidth="1"/>
+    <col min="1" max="1" width="12.4519230769231" style="25" customWidth="1"/>
+    <col min="2" max="2" width="22.0480769230769" style="25" customWidth="1"/>
+    <col min="3" max="3" width="37.2980769230769" style="25" customWidth="1"/>
+    <col min="4" max="4" width="10.8461538461538" style="25" customWidth="1"/>
+    <col min="5" max="5" width="14.5865384615385" style="25" customWidth="1"/>
+    <col min="6" max="16384" width="6" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
     </row>
     <row r="2" ht="14" customHeight="1" spans="1:5">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
+      <c r="A3" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
     </row>
     <row r="4" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-    </row>
-    <row r="11" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A11" s="22"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A13" s="22"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-    </row>
-    <row r="16" ht="14.25" customHeight="1" spans="1:5">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:5">
+      <c r="A11" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" ht="14" customHeight="1" spans="1:5">
+      <c r="A12" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="34"/>
+    </row>
+    <row r="13" ht="14" customHeight="1" spans="1:5">
+      <c r="A13" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="34"/>
+    </row>
+    <row r="14" ht="14" customHeight="1" spans="1:5">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+    </row>
+    <row r="15" ht="14" customHeight="1" spans="1:5">
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+    </row>
+    <row r="16" ht="14" customHeight="1" spans="1:5">
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
     </row>
     <row r="17" ht="14" customHeight="1" spans="1:5">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
     </row>
     <row r="18" ht="14" customHeight="1" spans="1:5">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
     </row>
     <row r="19" ht="14" customHeight="1" spans="1:5">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-    </row>
-    <row r="20" ht="14" customHeight="1" spans="1:5">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:5">
+      <c r="A20" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
     </row>
     <row r="21" ht="14" customHeight="1" spans="1:5">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
+      <c r="A21" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="36"/>
     </row>
     <row r="22" ht="14" customHeight="1" spans="1:5">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:5">
-      <c r="A23" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
+      <c r="A22" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="40"/>
+    </row>
+    <row r="23" ht="14" customHeight="1" spans="1:5">
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
     </row>
     <row r="24" ht="14" customHeight="1" spans="1:5">
-      <c r="A24" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="22"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
     </row>
     <row r="25" ht="14" customHeight="1" spans="1:5">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
     </row>
     <row r="26" ht="14" customHeight="1" spans="1:5">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
     </row>
     <row r="27" ht="14" customHeight="1" spans="1:5">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-    </row>
-    <row r="28" ht="14" customHeight="1" spans="1:5">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-    </row>
-    <row r="29" ht="14" customHeight="1" spans="1:5">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-    </row>
-    <row r="30" ht="14" customHeight="1" spans="1:5">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-    </row>
-    <row r="31" ht="14" customHeight="1" spans="1:5">
-      <c r="A31" s="22"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:5">
-      <c r="A32" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-    </row>
-    <row r="33" ht="14" customHeight="1" spans="1:5">
-      <c r="A33" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="E33" s="27"/>
-    </row>
-    <row r="34" ht="14" customHeight="1" spans="1:5">
-      <c r="A34" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E34" s="29"/>
-    </row>
-    <row r="35" ht="14" customHeight="1" spans="1:5">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-    </row>
-    <row r="36" ht="14" customHeight="1" spans="1:5">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-    </row>
-    <row r="37" ht="14" customHeight="1" spans="1:5">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-    </row>
-    <row r="38" ht="14" customHeight="1" spans="1:5">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-    </row>
-    <row r="39" ht="14" customHeight="1" spans="1:5">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="5">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
@@ -3218,7 +3236,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.9326923076923" customWidth="1"/>
@@ -3229,7 +3247,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B1" s="2">
         <v>20250101</v>
@@ -3241,7 +3259,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B2" s="5">
         <v>20280101</v>
@@ -3253,151 +3271,180 @@
     </row>
     <row r="3" ht="80" customHeight="1" spans="1:6">
       <c r="A3" s="7" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="15"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="10" t="s">
+      <c r="D4" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>63</v>
+      <c r="F4" s="10" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="11">
+      <c r="A5" s="12">
         <v>2025</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="13"/>
+      <c r="B5" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="13"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="11"/>
-      <c r="B7" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="F7" s="13"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="14"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="11"/>
-      <c r="B8" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="13"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="14"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="13"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="11">
+      <c r="A10" s="20">
         <v>2026</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="B10" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="22"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="14"/>
-      <c r="B11" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="14"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="23"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="23"/>
+      <c r="B14" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A5:A9"/>
-    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
